--- a/data/parentDaughterStats.xlsx
+++ b/data/parentDaughterStats.xlsx
@@ -447,49 +447,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>21.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>49.0</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51.0</t>
+          <t>23.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>10.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>44.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>45.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -501,27 +501,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.08424185874442916</t>
+          <t>0.1072695970040892</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.9788153193999705e-07</t>
+          <t>0.002959216626309653</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.13412809235751e-08</t>
+          <t>0.0013131884053420187</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.002841412330008307</t>
+          <t>0.012405987285776077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.604723600396763e-05</t>
+          <t>4.531635958482383e-06</t>
         </is>
       </c>
     </row>
@@ -569,22 +569,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>16.0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>14.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>45.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -596,54 +596,54 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>72.0</t>
+          <t>27.0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.0</t>
+          <t>29.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>63.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.0</t>
+          <t>20.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0.017661841268884787</t>
+          <t>0.06314473719271518</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.060756210938122106</t>
+          <t>0.015769748676575546</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.003923296561219859</t>
+          <t>0.1801888264678837</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.04067652410298299</t>
+          <t>0.00685909252933925</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.002171754837036133</t>
+          <t>0.000771939754486084</t>
         </is>
       </c>
     </row>

--- a/data/parentDaughterStats.xlsx
+++ b/data/parentDaughterStats.xlsx
@@ -457,22 +457,22 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>19.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17.0</t>
+          <t>18.0</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24.0</t>
+          <t>22.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10.0</t>
+          <t>11.0</t>
         </is>
       </c>
     </row>
@@ -489,22 +489,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>46.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.0</t>
+          <t>47.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>41.0</t>
+          <t>43.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>43.0</t>
         </is>
       </c>
     </row>
@@ -521,22 +521,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0005450419022237893</t>
+          <t>0.00021106516173760253</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.605328792403769e-05</t>
+          <t>0.00021106516173760253</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0231767371664556</t>
+          <t>0.006251273068244922</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.531635958482383e-06</t>
+          <t>7.00652872809293e-06</t>
         </is>
       </c>
     </row>
@@ -548,27 +548,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.10439041770829016</t>
+          <t>0.051501471193124516</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.0006703328934808283</t>
+          <t>0.00028323693414517237</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00026924148500789195</t>
+          <t>0.0004888347994197302</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00576228440133036</t>
+          <t>0.0016545981579813658</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.00012600858582683075</t>
+          <t>0.00013783356097592635</t>
         </is>
       </c>
     </row>
@@ -621,12 +621,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16.0</t>
+          <t>15.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15.0</t>
+          <t>13.0</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -653,12 +653,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>27.0</t>
+          <t>28.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -668,7 +668,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28.0</t>
+          <t>30.0</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -690,22 +690,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.0005450419022237893</t>
+          <t>0.00021106516173760253</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.605328792403769e-05</t>
+          <t>0.00021106516173760253</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0231767371664556</t>
+          <t>0.006251273068244922</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4.531635958482383e-06</t>
+          <t>7.00652872809293e-06</t>
         </is>
       </c>
     </row>
@@ -717,27 +717,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.04229642995073846</t>
+          <t>0.0176170758339822</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.01837957165412263</t>
+          <t>0.0015772383923149391</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01715882540338498</t>
+          <t>0.006472682714047551</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.03746996283143744</t>
+          <t>0.002811789242514351</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.00032937184195752493</t>
+          <t>0.00042879208575325166</t>
         </is>
       </c>
     </row>
